--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260626.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260626.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>133,095,000</t>
+          <t>119,589,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.33%</t>
+          <t>14.37%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,186,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.44%</t>
+          <t>7.96%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>1,743,000</t>
+          <t>1,591,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>5.50%</t>
         </is>
       </c>
     </row>
@@ -677,56 +677,56 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>10,790,000</t>
+          <t>10,140,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.55%</t>
+          <t>5.21%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>力成科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>21,621,000</t>
+          <t>4,412,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>力成科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,712,000</t>
+          <t>18,721,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.42%</t>
+          <t>4.31%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>5,967,000</t>
+          <t>5,193,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>7,813,000</t>
+          <t>8,164,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7,952,000</t>
+          <t>7,326,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -809,183 +809,183 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,135,000</t>
+          <t>18,463,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,793,000</t>
+          <t>8,415,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,655,000</t>
+          <t>2,543,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>15,094,000</t>
+          <t>12,917,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,170,000</t>
+          <t>12,645,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14,542,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>11,921,000</t>
+          <t>13,044,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>11,063,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>1,088,000</t>
+          <t>7,889,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1012,95 +1012,95 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>19,774,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>仁寶電腦</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>62,420,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>仁寶電腦</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,192,124,990</t>
+          <t>58,863,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>19,628,000</t>
+          <t>4,643,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1117,73 +1117,73 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>54,618,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>23,330,000</t>
+          <t>8,562,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>4,506,000</t>
+          <t>17,223,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>19,125,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,39 +1195,39 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,540,000</t>
+          <t>5,918,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,362,903,404</t>
+          <t>15,012,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,278,000</t>
+          <t>1,878,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,154 +1261,154 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,664,000</t>
+          <t>2,054,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,846,000</t>
+          <t>1,238,403,404</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>2,206,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>14,421,000</t>
+          <t>33,237,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>2,047,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,755,000</t>
+          <t>4,700,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,075,000</t>
+          <t>4,160,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1425,51 +1425,51 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>6,036,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>2,689,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>神基控股</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>6,222,000</t>
+          <t>7,706,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,308 +1481,792 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>長華電材</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>2,642,000</t>
+          <t>10,150,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>廣明光電</t>
+          <t>神基控股</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>7,462,000</t>
+          <t>4,549,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>廣明光電</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>9,012,000</t>
+          <t>5,765,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>矽創電子</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,276,000</t>
+          <t>546,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,673,000</t>
+          <t>3,111,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>瑞儀光電</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4,362,000</t>
+          <t>972,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>億光電子</t>
+          <t>瑞儀光電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>4,092,000</t>
+          <t>3,807,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>美律實業</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,440,000</t>
+          <t>323,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>中磊電子</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,315,000</t>
+          <t>2,895,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦媒體</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>295,000</t>
+          <t>634,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>是方電訊</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>159,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>崑鼎綠能</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>172,000</t>
+          <t>2,181,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>群光電能</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>216,000</t>
+          <t>1,952,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>矽創電子</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>951,000</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>亞翔工程</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>341,000</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>祥碩科技</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>209,000</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>神達控股</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>3,416,000</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>技嘉科技</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>898,000</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>微星科技</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>2,042,000</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>3023</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>信邦電子</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>883,000</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>8069</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>元太科技</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>1,371,000</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>鴻海精密</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>1,120,000</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>英業達股</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>3,718,000</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>億光電子</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>3,407,000</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>6191</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>精成科技</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>2,134,000</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>8112</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>至上電子</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>2,251,000</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>美律實業</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>2,161,000</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>中磊電子</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>1,901,000</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>5469</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>瀚宇博德</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>1,325,000</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>0.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>佳世達科</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>3,648,000</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>8454</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>富邦媒體</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>221,000</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>是方電訊</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>107,000</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>6803</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>崑鼎綠能</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>139,000</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>6412</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>群光電能</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>114,000</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
           <t>PFUR_NTD</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>-489,106,372</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>-0.34%</t>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>-78,692,550</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>DA_NTD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>-5,839,631,054</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>-4.28%</t>
         </is>
       </c>
     </row>
